--- a/rmonize/data_dictionary/DD_LISA_P1.xlsx
+++ b/rmonize/data_dictionary/DD_LISA_P1.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20415"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\Projekte\NFDI4Health\TA5\Pilotprojekte\Harmonisierung\HarmonizR\use-cases-harmonisation\rmonize\data_dictionary\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="K:\use-cases-harmonisation\rmonize\data_dictionary\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{30B8857A-D1A5-43D7-9D93-F1F7668B42E8}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8BE44F3B-8BED-40B1-A352-D418CC600C5B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12225" xr2:uid="{1200B70D-B446-4CDA-99A8-3FD394D791D2}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="11025" windowHeight="11760" activeTab="1" xr2:uid="{1200B70D-B446-4CDA-99A8-3FD394D791D2}"/>
   </bookViews>
   <sheets>
     <sheet name="Variables" sheetId="1" r:id="rId1"/>
@@ -26,10 +26,10 @@
         <xcalcf:feature name="microsoft.com:RD"/>
         <xcalcf:feature name="microsoft.com:Single"/>
         <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
         <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="334" uniqueCount="219">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="334" uniqueCount="214">
   <si>
     <t>index</t>
   </si>
@@ -639,27 +639,6 @@
     <t>female</t>
   </si>
   <si>
-    <t>No secondary school or elementary school certificate (Mother)</t>
-  </si>
-  <si>
-    <t>Lower secondary school or elementary school certificate (Mother)</t>
-  </si>
-  <si>
-    <t>Secondary school certificate (middle school leaving certificate)(Mother)</t>
-  </si>
-  <si>
-    <t>Completion of Polytechnic. high school (Mother)</t>
-  </si>
-  <si>
-    <t>Advanced technical college entrance qualification (Mother)</t>
-  </si>
-  <si>
-    <t>General or specialist university entrance qualification (Mother)</t>
-  </si>
-  <si>
-    <t>Other degree (Mother)</t>
-  </si>
-  <si>
     <t>No secondary school or elementary school certificate</t>
   </si>
   <si>
@@ -694,6 +673,12 @@
   </si>
   <si>
     <t>yes, less often</t>
+  </si>
+  <si>
+    <t>Other degree</t>
+  </si>
+  <si>
+    <t>General or specialist university entrance qualification</t>
   </si>
 </sst>
 </file>
@@ -804,7 +789,7 @@
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Standard" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -820,9 +805,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -860,7 +845,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -966,7 +951,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1108,7 +1093,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1117,7 +1102,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{08A73012-5CAD-43B9-A281-79101DF4E1E0}">
   <dimension ref="A1:D96"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="11.42578125" style="3"/>
     <col min="2" max="2" width="26.28515625" style="5" customWidth="1"/>
@@ -2478,7 +2463,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B7CFBFAA-22DC-428C-A718-7E0BADD40216}">
   <dimension ref="A1:D22"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="18.85546875" style="3" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="11.42578125" style="3"/>
@@ -2519,7 +2504,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="4" spans="1:4" ht="45" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="A4" s="6" t="s">
         <v>12</v>
       </c>
@@ -2530,7 +2515,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="5" spans="1:4" ht="45" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="A5" s="6" t="s">
         <v>12</v>
       </c>
@@ -2582,7 +2567,7 @@
         <v>6</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>205</v>
+        <v>213</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
@@ -2593,7 +2578,7 @@
         <v>7</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>206</v>
+        <v>212</v>
       </c>
     </row>
     <row r="11" spans="1:4" ht="30" x14ac:dyDescent="0.25">
@@ -2604,7 +2589,7 @@
         <v>1</v>
       </c>
       <c r="C11" s="9" t="s">
-        <v>207</v>
+        <v>200</v>
       </c>
     </row>
     <row r="12" spans="1:4" ht="30" x14ac:dyDescent="0.25">
@@ -2615,7 +2600,7 @@
         <v>2</v>
       </c>
       <c r="C12" s="10" t="s">
-        <v>208</v>
+        <v>201</v>
       </c>
     </row>
     <row r="13" spans="1:4" ht="45" x14ac:dyDescent="0.25">
@@ -2626,7 +2611,7 @@
         <v>3</v>
       </c>
       <c r="C13" s="10" t="s">
-        <v>209</v>
+        <v>202</v>
       </c>
     </row>
     <row r="14" spans="1:4" ht="30" x14ac:dyDescent="0.25">
@@ -2637,7 +2622,7 @@
         <v>4</v>
       </c>
       <c r="C14" s="10" t="s">
-        <v>210</v>
+        <v>203</v>
       </c>
     </row>
     <row r="15" spans="1:4" ht="30" x14ac:dyDescent="0.25">
@@ -2648,7 +2633,7 @@
         <v>5</v>
       </c>
       <c r="C15" s="10" t="s">
-        <v>211</v>
+        <v>204</v>
       </c>
     </row>
     <row r="16" spans="1:4" ht="30" x14ac:dyDescent="0.25">
@@ -2659,7 +2644,7 @@
         <v>6</v>
       </c>
       <c r="C16" s="10" t="s">
-        <v>212</v>
+        <v>205</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
@@ -2670,7 +2655,7 @@
         <v>7</v>
       </c>
       <c r="C17" s="8" t="s">
-        <v>213</v>
+        <v>206</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
@@ -2681,7 +2666,7 @@
         <v>1</v>
       </c>
       <c r="C18" t="s">
-        <v>214</v>
+        <v>207</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
@@ -2692,7 +2677,7 @@
         <v>2</v>
       </c>
       <c r="C19" s="14" t="s">
-        <v>215</v>
+        <v>208</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
@@ -2703,7 +2688,7 @@
         <v>3</v>
       </c>
       <c r="C20" s="14" t="s">
-        <v>216</v>
+        <v>209</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
@@ -2714,7 +2699,7 @@
         <v>4</v>
       </c>
       <c r="C21" s="14" t="s">
-        <v>217</v>
+        <v>210</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
@@ -2725,7 +2710,7 @@
         <v>5</v>
       </c>
       <c r="C22" s="14" t="s">
-        <v>218</v>
+        <v>211</v>
       </c>
     </row>
   </sheetData>
@@ -2734,15 +2719,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <Zeit xmlns="b63cdcf7-47fa-43f6-87e5-23b415b5c413" xsi:nil="true"/>
@@ -2752,6 +2728,15 @@
     <TaxCatchAll xmlns="12535b08-222e-45d2-b6db-15019f1afee6" xsi:nil="true"/>
   </documentManagement>
 </p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2996,14 +2981,6 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4C05FF1B-7508-40EF-8319-E993EA07F007}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1D9CBEFE-8C4C-4054-8E02-CA457E93B4C8}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
@@ -3016,6 +2993,14 @@
     <ds:schemaRef ds:uri="12535b08-222e-45d2-b6db-15019f1afee6"/>
     <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
     <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4C05FF1B-7508-40EF-8319-E993EA07F007}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>

--- a/rmonize/data_dictionary/DD_LISA_P1.xlsx
+++ b/rmonize/data_dictionary/DD_LISA_P1.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20417"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="K:\use-cases-harmonisation\rmonize\data_dictionary\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\schwarz-f\Desktop\use-cases-harmonisation\rmonize\data_dictionary\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8BE44F3B-8BED-40B1-A352-D418CC600C5B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6E56B011-2104-47B2-BF3F-F9151EEF0E4A}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="11025" windowHeight="11760" activeTab="1" xr2:uid="{1200B70D-B446-4CDA-99A8-3FD394D791D2}"/>
   </bookViews>
@@ -21,23 +21,12 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="334" uniqueCount="214">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="372" uniqueCount="224">
   <si>
     <t>index</t>
   </si>
@@ -639,27 +628,6 @@
     <t>female</t>
   </si>
   <si>
-    <t>No secondary school or elementary school certificate</t>
-  </si>
-  <si>
-    <t>Lower secondary school or elementary school certificate</t>
-  </si>
-  <si>
-    <t>Secondary school certificate (middle school leaving certificate)</t>
-  </si>
-  <si>
-    <t>Completion of Polytechnic. high school</t>
-  </si>
-  <si>
-    <t>Advanced technical college entrance qualification</t>
-  </si>
-  <si>
-    <t>general or specialist university entrance qualification</t>
-  </si>
-  <si>
-    <t>other degree</t>
-  </si>
-  <si>
     <t>no</t>
   </si>
   <si>
@@ -675,10 +643,61 @@
     <t>yes, less often</t>
   </si>
   <si>
-    <t>Other degree</t>
-  </si>
-  <si>
-    <t>General or specialist university entrance qualification</t>
+    <t>kein Haupt- oder Volksschulabschluss</t>
+  </si>
+  <si>
+    <t>Haupt- oder Volksschulabschluss</t>
+  </si>
+  <si>
+    <t>Realschulabschluss (mittlere Reife)</t>
+  </si>
+  <si>
+    <t>Abschluss der Polytechn. Oberschule</t>
+  </si>
+  <si>
+    <t>Fachhochschulreife</t>
+  </si>
+  <si>
+    <t>allgem. oder fachgeb. Hochschulreife</t>
+  </si>
+  <si>
+    <t>anderer Abschluss</t>
+  </si>
+  <si>
+    <t>MUTBERU_0</t>
+  </si>
+  <si>
+    <t>VATBERU_0</t>
+  </si>
+  <si>
+    <t>highest job qualification of the mother</t>
+  </si>
+  <si>
+    <t>highest job qualification of the father</t>
+  </si>
+  <si>
+    <t>abgeschlossene beruflich-schulische Ausbildung</t>
+  </si>
+  <si>
+    <t>abgeschlossene Ausbildung an Fachschule</t>
+  </si>
+  <si>
+    <t>Fachhochschulabschluss</t>
+  </si>
+  <si>
+    <t>Hochschulabschluss</t>
+  </si>
+  <si>
+    <t>anderer beruflicher Abschluss</t>
+  </si>
+  <si>
+    <t>abgeschlossene beruflich-betriebliche Ausbildung</t>
+  </si>
+  <si>
+    <t>kein beruflicher Abschluss</t>
+  </si>
+  <si>
+    <t>Auszubildende/r, Student/in</t>
   </si>
 </sst>
 </file>
@@ -747,7 +766,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -773,12 +792,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top" wrapText="1"/>
     </xf>
@@ -789,7 +802,7 @@
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Standard" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -805,9 +818,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office">
   <a:themeElements>
-    <a:clrScheme name="Office 2013 - 2022">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -845,7 +858,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2013 - 2022">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -951,7 +964,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2013 - 2022">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1093,7 +1106,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1101,8 +1114,8 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{08A73012-5CAD-43B9-A281-79101DF4E1E0}">
-  <dimension ref="A1:D96"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:D98"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="11.42578125" style="3"/>
     <col min="2" max="2" width="26.28515625" style="5" customWidth="1"/>
@@ -1198,28 +1211,28 @@
       <c r="A7">
         <v>6</v>
       </c>
-      <c r="B7" t="s">
-        <v>16</v>
+      <c r="B7" s="5" t="s">
+        <v>212</v>
       </c>
       <c r="C7" t="s">
-        <v>17</v>
-      </c>
-      <c r="D7" t="s">
-        <v>18</v>
+        <v>214</v>
+      </c>
+      <c r="D7" s="5" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>7</v>
       </c>
-      <c r="B8" t="s">
-        <v>19</v>
-      </c>
-      <c r="C8" t="s">
-        <v>20</v>
-      </c>
-      <c r="D8" t="s">
-        <v>18</v>
+      <c r="B8" s="5" t="s">
+        <v>213</v>
+      </c>
+      <c r="C8" s="7" t="s">
+        <v>215</v>
+      </c>
+      <c r="D8" s="5" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
@@ -1227,10 +1240,10 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="C9" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="D9" t="s">
         <v>18</v>
@@ -1241,10 +1254,10 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="C10" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="D10" t="s">
         <v>18</v>
@@ -1255,10 +1268,10 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="C11" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="D11" t="s">
         <v>18</v>
@@ -1269,10 +1282,10 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="C12" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="D12" t="s">
         <v>18</v>
@@ -1283,13 +1296,13 @@
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="C13" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="D13" t="s">
-        <v>9</v>
+        <v>18</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
@@ -1297,10 +1310,10 @@
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>31</v>
-      </c>
-      <c r="C14" s="12" t="s">
-        <v>32</v>
+        <v>27</v>
+      </c>
+      <c r="C14" t="s">
+        <v>28</v>
       </c>
       <c r="D14" t="s">
         <v>18</v>
@@ -1311,13 +1324,13 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="C15" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="D15" t="s">
-        <v>18</v>
+        <v>9</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
@@ -1325,10 +1338,10 @@
         <v>15</v>
       </c>
       <c r="B16" t="s">
-        <v>35</v>
-      </c>
-      <c r="C16" t="s">
-        <v>36</v>
+        <v>31</v>
+      </c>
+      <c r="C16" s="10" t="s">
+        <v>32</v>
       </c>
       <c r="D16" t="s">
         <v>18</v>
@@ -1339,10 +1352,10 @@
         <v>16</v>
       </c>
       <c r="B17" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="C17" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="D17" t="s">
         <v>18</v>
@@ -1353,10 +1366,10 @@
         <v>17</v>
       </c>
       <c r="B18" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="C18" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="D18" t="s">
         <v>18</v>
@@ -1367,10 +1380,10 @@
         <v>18</v>
       </c>
       <c r="B19" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="C19" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="D19" t="s">
         <v>18</v>
@@ -1381,10 +1394,10 @@
         <v>19</v>
       </c>
       <c r="B20" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="C20" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="D20" t="s">
         <v>18</v>
@@ -1395,10 +1408,10 @@
         <v>20</v>
       </c>
       <c r="B21" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="C21" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="D21" t="s">
         <v>18</v>
@@ -1409,10 +1422,10 @@
         <v>21</v>
       </c>
       <c r="B22" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="C22" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="D22" t="s">
         <v>18</v>
@@ -1423,10 +1436,10 @@
         <v>22</v>
       </c>
       <c r="B23" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="C23" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="D23" t="s">
         <v>18</v>
@@ -1437,10 +1450,10 @@
         <v>23</v>
       </c>
       <c r="B24" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="C24" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="D24" t="s">
         <v>18</v>
@@ -1451,10 +1464,10 @@
         <v>24</v>
       </c>
       <c r="B25" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="C25" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="D25" t="s">
         <v>18</v>
@@ -1465,10 +1478,10 @@
         <v>25</v>
       </c>
       <c r="B26" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="C26" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="D26" t="s">
         <v>18</v>
@@ -1479,10 +1492,10 @@
         <v>26</v>
       </c>
       <c r="B27" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="C27" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D27" t="s">
         <v>18</v>
@@ -1493,10 +1506,10 @@
         <v>27</v>
       </c>
       <c r="B28" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="C28" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="D28" t="s">
         <v>18</v>
@@ -1507,10 +1520,10 @@
         <v>28</v>
       </c>
       <c r="B29" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="C29" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="D29" t="s">
         <v>18</v>
@@ -1521,10 +1534,10 @@
         <v>29</v>
       </c>
       <c r="B30" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="C30" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="D30" t="s">
         <v>18</v>
@@ -1535,10 +1548,10 @@
         <v>30</v>
       </c>
       <c r="B31" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="C31" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="D31" t="s">
         <v>18</v>
@@ -1549,10 +1562,10 @@
         <v>31</v>
       </c>
       <c r="B32" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="C32" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="D32" t="s">
         <v>18</v>
@@ -1563,10 +1576,10 @@
         <v>32</v>
       </c>
       <c r="B33" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="C33" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="D33" t="s">
         <v>18</v>
@@ -1577,10 +1590,10 @@
         <v>33</v>
       </c>
       <c r="B34" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="C34" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="D34" t="s">
         <v>18</v>
@@ -1591,10 +1604,10 @@
         <v>34</v>
       </c>
       <c r="B35" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="C35" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="D35" t="s">
         <v>18</v>
@@ -1605,10 +1618,10 @@
         <v>35</v>
       </c>
       <c r="B36" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="C36" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="D36" t="s">
         <v>18</v>
@@ -1619,10 +1632,10 @@
         <v>36</v>
       </c>
       <c r="B37" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="C37" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="D37" t="s">
         <v>18</v>
@@ -1633,10 +1646,10 @@
         <v>37</v>
       </c>
       <c r="B38" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="C38" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="D38" t="s">
         <v>18</v>
@@ -1647,10 +1660,10 @@
         <v>38</v>
       </c>
       <c r="B39" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="C39" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="D39" t="s">
         <v>18</v>
@@ -1661,10 +1674,10 @@
         <v>39</v>
       </c>
       <c r="B40" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="C40" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="D40" t="s">
         <v>18</v>
@@ -1675,10 +1688,10 @@
         <v>40</v>
       </c>
       <c r="B41" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="C41" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="D41" t="s">
         <v>18</v>
@@ -1689,10 +1702,10 @@
         <v>41</v>
       </c>
       <c r="B42" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="C42" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="D42" t="s">
         <v>18</v>
@@ -1703,10 +1716,10 @@
         <v>42</v>
       </c>
       <c r="B43" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="C43" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="D43" t="s">
         <v>18</v>
@@ -1717,10 +1730,10 @@
         <v>43</v>
       </c>
       <c r="B44" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="C44" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="D44" t="s">
         <v>18</v>
@@ -1731,10 +1744,10 @@
         <v>44</v>
       </c>
       <c r="B45" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="C45" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="D45" t="s">
         <v>18</v>
@@ -1745,10 +1758,10 @@
         <v>45</v>
       </c>
       <c r="B46" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="C46" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="D46" t="s">
         <v>18</v>
@@ -1759,10 +1772,10 @@
         <v>46</v>
       </c>
       <c r="B47" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="C47" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="D47" t="s">
         <v>18</v>
@@ -1773,10 +1786,10 @@
         <v>47</v>
       </c>
       <c r="B48" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="C48" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="D48" t="s">
         <v>18</v>
@@ -1787,10 +1800,10 @@
         <v>48</v>
       </c>
       <c r="B49" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="C49" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="D49" t="s">
         <v>18</v>
@@ -1801,10 +1814,10 @@
         <v>49</v>
       </c>
       <c r="B50" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="C50" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="D50" t="s">
         <v>18</v>
@@ -1815,10 +1828,10 @@
         <v>50</v>
       </c>
       <c r="B51" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C51" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="D51" t="s">
         <v>18</v>
@@ -1829,10 +1842,10 @@
         <v>51</v>
       </c>
       <c r="B52" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="C52" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="D52" t="s">
         <v>18</v>
@@ -1843,10 +1856,10 @@
         <v>52</v>
       </c>
       <c r="B53" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="C53" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="D53" t="s">
         <v>18</v>
@@ -1857,10 +1870,10 @@
         <v>53</v>
       </c>
       <c r="B54" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="C54" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="D54" t="s">
         <v>18</v>
@@ -1871,10 +1884,10 @@
         <v>54</v>
       </c>
       <c r="B55" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="C55" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="D55" t="s">
         <v>18</v>
@@ -1885,10 +1898,10 @@
         <v>55</v>
       </c>
       <c r="B56" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="C56" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="D56" t="s">
         <v>18</v>
@@ -1899,10 +1912,10 @@
         <v>56</v>
       </c>
       <c r="B57" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="C57" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="D57" t="s">
         <v>18</v>
@@ -1913,10 +1926,10 @@
         <v>57</v>
       </c>
       <c r="B58" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="C58" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="D58" t="s">
         <v>18</v>
@@ -1927,10 +1940,10 @@
         <v>58</v>
       </c>
       <c r="B59" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="C59" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="D59" t="s">
         <v>18</v>
@@ -1941,10 +1954,10 @@
         <v>59</v>
       </c>
       <c r="B60" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="C60" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="D60" t="s">
         <v>18</v>
@@ -1955,10 +1968,10 @@
         <v>60</v>
       </c>
       <c r="B61" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="C61" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="D61" t="s">
         <v>18</v>
@@ -1969,10 +1982,10 @@
         <v>61</v>
       </c>
       <c r="B62" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="C62" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="D62" t="s">
         <v>18</v>
@@ -1983,10 +1996,10 @@
         <v>62</v>
       </c>
       <c r="B63" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="C63" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="D63" t="s">
         <v>18</v>
@@ -1997,10 +2010,10 @@
         <v>63</v>
       </c>
       <c r="B64" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="C64" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="D64" t="s">
         <v>18</v>
@@ -2011,10 +2024,10 @@
         <v>64</v>
       </c>
       <c r="B65" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="C65" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="D65" t="s">
         <v>18</v>
@@ -2025,10 +2038,10 @@
         <v>65</v>
       </c>
       <c r="B66" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="C66" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="D66" t="s">
         <v>18</v>
@@ -2039,10 +2052,10 @@
         <v>66</v>
       </c>
       <c r="B67" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="C67" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="D67" t="s">
         <v>18</v>
@@ -2053,10 +2066,10 @@
         <v>67</v>
       </c>
       <c r="B68" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="C68" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="D68" t="s">
         <v>18</v>
@@ -2067,10 +2080,10 @@
         <v>68</v>
       </c>
       <c r="B69" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="C69" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="D69" t="s">
         <v>18</v>
@@ -2081,10 +2094,10 @@
         <v>69</v>
       </c>
       <c r="B70" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="C70" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="D70" t="s">
         <v>18</v>
@@ -2095,10 +2108,10 @@
         <v>70</v>
       </c>
       <c r="B71" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="C71" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="D71" t="s">
         <v>18</v>
@@ -2109,10 +2122,10 @@
         <v>71</v>
       </c>
       <c r="B72" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="C72" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="D72" t="s">
         <v>18</v>
@@ -2123,10 +2136,10 @@
         <v>72</v>
       </c>
       <c r="B73" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="C73" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="D73" t="s">
         <v>18</v>
@@ -2137,10 +2150,10 @@
         <v>73</v>
       </c>
       <c r="B74" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="C74" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="D74" t="s">
         <v>18</v>
@@ -2151,10 +2164,10 @@
         <v>74</v>
       </c>
       <c r="B75" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="C75" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="D75" t="s">
         <v>18</v>
@@ -2165,10 +2178,10 @@
         <v>75</v>
       </c>
       <c r="B76" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="C76" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="D76" t="s">
         <v>18</v>
@@ -2179,10 +2192,10 @@
         <v>76</v>
       </c>
       <c r="B77" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="C77" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="D77" t="s">
         <v>18</v>
@@ -2193,10 +2206,10 @@
         <v>77</v>
       </c>
       <c r="B78" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="C78" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="D78" t="s">
         <v>18</v>
@@ -2207,10 +2220,10 @@
         <v>78</v>
       </c>
       <c r="B79" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="C79" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="D79" t="s">
         <v>18</v>
@@ -2221,10 +2234,10 @@
         <v>79</v>
       </c>
       <c r="B80" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="C80" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="D80" t="s">
         <v>18</v>
@@ -2235,10 +2248,10 @@
         <v>80</v>
       </c>
       <c r="B81" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="C81" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="D81" t="s">
         <v>18</v>
@@ -2249,10 +2262,10 @@
         <v>81</v>
       </c>
       <c r="B82" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="C82" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="D82" t="s">
         <v>18</v>
@@ -2263,10 +2276,10 @@
         <v>82</v>
       </c>
       <c r="B83" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="C83" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="D83" t="s">
         <v>18</v>
@@ -2277,10 +2290,10 @@
         <v>83</v>
       </c>
       <c r="B84" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="C84" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="D84" t="s">
         <v>18</v>
@@ -2291,10 +2304,10 @@
         <v>84</v>
       </c>
       <c r="B85" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="C85" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="D85" t="s">
         <v>18</v>
@@ -2305,10 +2318,10 @@
         <v>85</v>
       </c>
       <c r="B86" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="C86" t="s">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="D86" t="s">
         <v>18</v>
@@ -2319,10 +2332,10 @@
         <v>86</v>
       </c>
       <c r="B87" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="C87" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="D87" t="s">
         <v>18</v>
@@ -2333,10 +2346,10 @@
         <v>87</v>
       </c>
       <c r="B88" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="C88" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="D88" t="s">
         <v>18</v>
@@ -2347,10 +2360,10 @@
         <v>88</v>
       </c>
       <c r="B89" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="C89" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="D89" t="s">
         <v>18</v>
@@ -2360,11 +2373,11 @@
       <c r="A90">
         <v>89</v>
       </c>
-      <c r="B90" s="12" t="s">
-        <v>183</v>
+      <c r="B90" t="s">
+        <v>179</v>
       </c>
       <c r="C90" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="D90" t="s">
         <v>18</v>
@@ -2375,10 +2388,10 @@
         <v>90</v>
       </c>
       <c r="B91" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="C91" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="D91" t="s">
         <v>18</v>
@@ -2388,11 +2401,11 @@
       <c r="A92">
         <v>91</v>
       </c>
-      <c r="B92" t="s">
-        <v>187</v>
+      <c r="B92" s="10" t="s">
+        <v>183</v>
       </c>
       <c r="C92" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="D92" t="s">
         <v>18</v>
@@ -2403,10 +2416,10 @@
         <v>92</v>
       </c>
       <c r="B93" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="C93" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="D93" t="s">
         <v>18</v>
@@ -2417,10 +2430,10 @@
         <v>93</v>
       </c>
       <c r="B94" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
       <c r="C94" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="D94" t="s">
         <v>18</v>
@@ -2431,10 +2444,10 @@
         <v>94</v>
       </c>
       <c r="B95" t="s">
-        <v>193</v>
-      </c>
-      <c r="C95" s="13" t="s">
-        <v>194</v>
+        <v>189</v>
+      </c>
+      <c r="C95" t="s">
+        <v>190</v>
       </c>
       <c r="D95" t="s">
         <v>18</v>
@@ -2445,12 +2458,40 @@
         <v>95</v>
       </c>
       <c r="B96" t="s">
+        <v>191</v>
+      </c>
+      <c r="C96" t="s">
+        <v>192</v>
+      </c>
+      <c r="D96" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="97" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A97">
+        <v>96</v>
+      </c>
+      <c r="B97" t="s">
+        <v>193</v>
+      </c>
+      <c r="C97" s="11" t="s">
+        <v>194</v>
+      </c>
+      <c r="D97" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="98" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A98">
+        <v>97</v>
+      </c>
+      <c r="B98" t="s">
         <v>195</v>
       </c>
-      <c r="C96" t="s">
+      <c r="C98" t="s">
         <v>196</v>
       </c>
-      <c r="D96" t="s">
+      <c r="D98" t="s">
         <v>18</v>
       </c>
     </row>
@@ -2462,12 +2503,12 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B7CFBFAA-22DC-428C-A718-7E0BADD40216}">
-  <dimension ref="A1:D22"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:D38"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="18.85546875" style="3" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="11.42578125" style="3"/>
-    <col min="3" max="3" width="30.5703125" style="5" customWidth="1"/>
+    <col min="3" max="3" width="46.28515625" style="5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -2504,7 +2545,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="4" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="6" t="s">
         <v>12</v>
       </c>
@@ -2512,10 +2553,10 @@
         <v>1</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" s="6" t="s">
         <v>12</v>
       </c>
@@ -2523,10 +2564,10 @@
         <v>2</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>201</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" ht="45" x14ac:dyDescent="0.25">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" s="6" t="s">
         <v>12</v>
       </c>
@@ -2534,10 +2575,10 @@
         <v>3</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" s="6" t="s">
         <v>12</v>
       </c>
@@ -2545,10 +2586,10 @@
         <v>4</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" s="6" t="s">
         <v>12</v>
       </c>
@@ -2556,10 +2597,10 @@
         <v>5</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" s="6" t="s">
         <v>12</v>
       </c>
@@ -2567,7 +2608,7 @@
         <v>6</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
@@ -2578,84 +2619,84 @@
         <v>7</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>14</v>
       </c>
-      <c r="B11" s="11">
+      <c r="B11" s="9">
         <v>1</v>
       </c>
-      <c r="C11" s="9" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+      <c r="C11" s="5" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>14</v>
       </c>
-      <c r="B12" s="11">
+      <c r="B12" s="9">
         <v>2</v>
       </c>
-      <c r="C12" s="10" t="s">
-        <v>201</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" ht="45" x14ac:dyDescent="0.25">
+      <c r="C12" s="5" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>14</v>
       </c>
-      <c r="B13" s="11">
+      <c r="B13" s="9">
         <v>3</v>
       </c>
-      <c r="C13" s="10" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+      <c r="C13" s="5" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>14</v>
       </c>
-      <c r="B14" s="11">
+      <c r="B14" s="9">
         <v>4</v>
       </c>
-      <c r="C14" s="10" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+      <c r="C14" s="5" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>14</v>
       </c>
-      <c r="B15" s="11">
+      <c r="B15" s="9">
         <v>5</v>
       </c>
-      <c r="C15" s="10" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+      <c r="C15" s="5" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>14</v>
       </c>
-      <c r="B16" s="11">
+      <c r="B16" s="9">
         <v>6</v>
       </c>
-      <c r="C16" s="10" t="s">
-        <v>205</v>
+      <c r="C16" s="5" t="s">
+        <v>210</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>14</v>
       </c>
-      <c r="B17" s="11">
+      <c r="B17" s="9">
         <v>7</v>
       </c>
-      <c r="C17" s="8" t="s">
-        <v>206</v>
+      <c r="C17" s="5" t="s">
+        <v>211</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
@@ -2666,51 +2707,227 @@
         <v>1</v>
       </c>
       <c r="C18" t="s">
-        <v>207</v>
+        <v>200</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>29</v>
       </c>
-      <c r="B19" s="11">
+      <c r="B19" s="9">
         <v>2</v>
       </c>
-      <c r="C19" s="14" t="s">
-        <v>208</v>
+      <c r="C19" s="12" t="s">
+        <v>201</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>29</v>
       </c>
-      <c r="B20" s="11">
+      <c r="B20" s="9">
         <v>3</v>
       </c>
-      <c r="C20" s="14" t="s">
-        <v>209</v>
+      <c r="C20" s="12" t="s">
+        <v>202</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>29</v>
       </c>
-      <c r="B21" s="11">
+      <c r="B21" s="9">
         <v>4</v>
       </c>
-      <c r="C21" s="14" t="s">
-        <v>210</v>
+      <c r="C21" s="12" t="s">
+        <v>203</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>29</v>
       </c>
-      <c r="B22" s="11">
+      <c r="B22" s="9">
         <v>5</v>
       </c>
-      <c r="C22" s="14" t="s">
-        <v>211</v>
+      <c r="C22" s="12" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A23" s="5" t="s">
+        <v>212</v>
+      </c>
+      <c r="B23" s="3">
+        <v>1</v>
+      </c>
+      <c r="C23" s="5" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A24" s="5" t="s">
+        <v>212</v>
+      </c>
+      <c r="B24" s="3">
+        <v>2</v>
+      </c>
+      <c r="C24" s="5" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+      <c r="A25" s="5" t="s">
+        <v>212</v>
+      </c>
+      <c r="B25" s="3">
+        <v>3</v>
+      </c>
+      <c r="C25" s="5" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+      <c r="A26" s="5" t="s">
+        <v>212</v>
+      </c>
+      <c r="B26" s="3">
+        <v>4</v>
+      </c>
+      <c r="C26" s="5" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+      <c r="A27" s="5" t="s">
+        <v>212</v>
+      </c>
+      <c r="B27" s="3">
+        <v>5</v>
+      </c>
+      <c r="C27" s="5" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A28" s="5" t="s">
+        <v>212</v>
+      </c>
+      <c r="B28" s="3">
+        <v>6</v>
+      </c>
+      <c r="C28" s="5" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A29" s="5" t="s">
+        <v>212</v>
+      </c>
+      <c r="B29" s="3">
+        <v>7</v>
+      </c>
+      <c r="C29" s="5" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A30" s="5" t="s">
+        <v>212</v>
+      </c>
+      <c r="B30" s="3">
+        <v>8</v>
+      </c>
+      <c r="C30" s="5" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A31" s="5" t="s">
+        <v>213</v>
+      </c>
+      <c r="B31" s="3">
+        <v>1</v>
+      </c>
+      <c r="C31" s="5" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A32" s="5" t="s">
+        <v>213</v>
+      </c>
+      <c r="B32" s="3">
+        <v>2</v>
+      </c>
+      <c r="C32" s="5" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+      <c r="A33" s="5" t="s">
+        <v>213</v>
+      </c>
+      <c r="B33" s="3">
+        <v>3</v>
+      </c>
+      <c r="C33" s="5" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+      <c r="A34" s="5" t="s">
+        <v>213</v>
+      </c>
+      <c r="B34" s="3">
+        <v>4</v>
+      </c>
+      <c r="C34" s="5" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+      <c r="A35" s="5" t="s">
+        <v>213</v>
+      </c>
+      <c r="B35" s="3">
+        <v>5</v>
+      </c>
+      <c r="C35" s="5" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A36" s="5" t="s">
+        <v>213</v>
+      </c>
+      <c r="B36" s="3">
+        <v>6</v>
+      </c>
+      <c r="C36" s="5" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A37" s="5" t="s">
+        <v>213</v>
+      </c>
+      <c r="B37" s="3">
+        <v>7</v>
+      </c>
+      <c r="C37" s="5" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A38" s="5" t="s">
+        <v>213</v>
+      </c>
+      <c r="B38" s="3">
+        <v>8</v>
+      </c>
+      <c r="C38" s="5" t="s">
+        <v>220</v>
       </c>
     </row>
   </sheetData>
@@ -2719,27 +2936,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <Zeit xmlns="b63cdcf7-47fa-43f6-87e5-23b415b5c413" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="b63cdcf7-47fa-43f6-87e5-23b415b5c413">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="12535b08-222e-45d2-b6db-15019f1afee6" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Dokument" ma:contentTypeID="0x010100B1DC67C611DD5E4D81775F9F3E26A7B2" ma:contentTypeVersion="16" ma:contentTypeDescription="Ein neues Dokument erstellen." ma:contentTypeScope="" ma:versionID="7f379a5812b480a74f9d031be5f88a83">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="b63cdcf7-47fa-43f6-87e5-23b415b5c413" xmlns:ns3="12535b08-222e-45d2-b6db-15019f1afee6" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="dbce1e37d7de67e1c835013ca0ee7a7c" ns2:_="" ns3:_="">
     <xsd:import namespace="b63cdcf7-47fa-43f6-87e5-23b415b5c413"/>
@@ -2980,32 +3176,28 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1D9CBEFE-8C4C-4054-8E02-CA457E93B4C8}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="b63cdcf7-47fa-43f6-87e5-23b415b5c413"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="12535b08-222e-45d2-b6db-15019f1afee6"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4C05FF1B-7508-40EF-8319-E993EA07F007}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <Zeit xmlns="b63cdcf7-47fa-43f6-87e5-23b415b5c413" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="b63cdcf7-47fa-43f6-87e5-23b415b5c413">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="12535b08-222e-45d2-b6db-15019f1afee6" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4E15759D-0549-4559-B749-E28DD96246FA}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -3022,4 +3214,29 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4C05FF1B-7508-40EF-8319-E993EA07F007}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1D9CBEFE-8C4C-4054-8E02-CA457E93B4C8}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="b63cdcf7-47fa-43f6-87e5-23b415b5c413"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="12535b08-222e-45d2-b6db-15019f1afee6"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/rmonize/data_dictionary/DD_LISA_P1.xlsx
+++ b/rmonize/data_dictionary/DD_LISA_P1.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20417"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\schwarz-f\Desktop\use-cases-harmonisation\rmonize\data_dictionary\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6E56B011-2104-47B2-BF3F-F9151EEF0E4A}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CFB9BBEC-D947-4E83-9C27-711AAFCCE65C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="11025" windowHeight="11760" activeTab="1" xr2:uid="{1200B70D-B446-4CDA-99A8-3FD394D791D2}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{1200B70D-B446-4CDA-99A8-3FD394D791D2}"/>
   </bookViews>
   <sheets>
     <sheet name="Variables" sheetId="1" r:id="rId1"/>
@@ -20,6 +20,9 @@
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
     </ext>
   </extLst>
 </workbook>
@@ -766,11 +769,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
@@ -818,9 +818,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 – 2022-Design">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 – 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -858,7 +858,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 – 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -964,7 +964,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 – 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1106,7 +1106,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1117,10 +1117,10 @@
   <dimension ref="A1:D98"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="11.42578125" style="3"/>
-    <col min="2" max="2" width="26.28515625" style="5" customWidth="1"/>
-    <col min="3" max="3" width="157.5703125" style="5" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.5703125" style="5"/>
+    <col min="1" max="1" width="11.42578125" style="2"/>
+    <col min="2" max="2" width="26.28515625" style="4" customWidth="1"/>
+    <col min="3" max="3" width="157.5703125" style="4" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.5703125" style="4"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -1200,10 +1200,10 @@
       <c r="B6" t="s">
         <v>14</v>
       </c>
-      <c r="C6" s="7" t="s">
+      <c r="C6" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="D6" s="8" t="s">
+      <c r="D6" s="7" t="s">
         <v>9</v>
       </c>
     </row>
@@ -1211,13 +1211,13 @@
       <c r="A7">
         <v>6</v>
       </c>
-      <c r="B7" s="5" t="s">
+      <c r="B7" s="4" t="s">
         <v>212</v>
       </c>
       <c r="C7" t="s">
         <v>214</v>
       </c>
-      <c r="D7" s="5" t="s">
+      <c r="D7" s="4" t="s">
         <v>9</v>
       </c>
     </row>
@@ -1225,13 +1225,13 @@
       <c r="A8">
         <v>7</v>
       </c>
-      <c r="B8" s="5" t="s">
+      <c r="B8" s="4" t="s">
         <v>213</v>
       </c>
-      <c r="C8" s="7" t="s">
+      <c r="C8" s="6" t="s">
         <v>215</v>
       </c>
-      <c r="D8" s="5" t="s">
+      <c r="D8" s="4" t="s">
         <v>9</v>
       </c>
     </row>
@@ -1340,7 +1340,7 @@
       <c r="B16" t="s">
         <v>31</v>
       </c>
-      <c r="C16" s="10" t="s">
+      <c r="C16" s="9" t="s">
         <v>32</v>
       </c>
       <c r="D16" t="s">
@@ -2401,7 +2401,7 @@
       <c r="A92">
         <v>91</v>
       </c>
-      <c r="B92" s="10" t="s">
+      <c r="B92" s="9" t="s">
         <v>183</v>
       </c>
       <c r="C92" t="s">
@@ -2474,7 +2474,7 @@
       <c r="B97" t="s">
         <v>193</v>
       </c>
-      <c r="C97" s="11" t="s">
+      <c r="C97" s="10" t="s">
         <v>194</v>
       </c>
       <c r="D97" t="s">
@@ -2503,188 +2503,187 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B7CFBFAA-22DC-428C-A718-7E0BADD40216}">
-  <dimension ref="A1:D38"/>
+  <dimension ref="A1:C38"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="18.85546875" style="3" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11.42578125" style="3"/>
-    <col min="3" max="3" width="46.28515625" style="5" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="18.85546875" style="2" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.42578125" style="2"/>
+    <col min="3" max="3" width="46.28515625" style="4" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1" s="2" t="s">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
         <v>197</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="4" t="s">
+      <c r="C1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1"/>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A2" s="3" t="s">
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="B2" s="3">
+      <c r="B2" s="2">
         <v>1</v>
       </c>
-      <c r="C2" s="5" t="s">
+      <c r="C2" s="4" t="s">
         <v>198</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A3" s="3" t="s">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="B3" s="3">
+      <c r="B3" s="2">
         <v>2</v>
       </c>
-      <c r="C3" s="5" t="s">
+      <c r="C3" s="4" t="s">
         <v>199</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A4" s="6" t="s">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="B4" s="3">
+      <c r="B4" s="2">
         <v>1</v>
       </c>
-      <c r="C4" s="5" t="s">
+      <c r="C4" s="4" t="s">
         <v>205</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A5" s="6" t="s">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="B5" s="3">
+      <c r="B5" s="2">
         <v>2</v>
       </c>
-      <c r="C5" s="5" t="s">
+      <c r="C5" s="4" t="s">
         <v>206</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A6" s="6" t="s">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="B6" s="3">
+      <c r="B6" s="2">
         <v>3</v>
       </c>
-      <c r="C6" s="5" t="s">
+      <c r="C6" s="4" t="s">
         <v>207</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A7" s="6" t="s">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A7" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="B7" s="3">
+      <c r="B7" s="2">
         <v>4</v>
       </c>
-      <c r="C7" s="5" t="s">
+      <c r="C7" s="4" t="s">
         <v>208</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A8" s="6" t="s">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A8" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="B8" s="3">
+      <c r="B8" s="2">
         <v>5</v>
       </c>
-      <c r="C8" s="5" t="s">
+      <c r="C8" s="4" t="s">
         <v>209</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A9" s="6" t="s">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A9" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="B9" s="3">
+      <c r="B9" s="2">
         <v>6</v>
       </c>
-      <c r="C9" s="5" t="s">
+      <c r="C9" s="4" t="s">
         <v>210</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A10" s="6" t="s">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A10" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="B10" s="3">
+      <c r="B10" s="2">
         <v>7</v>
       </c>
-      <c r="C10" s="5" t="s">
+      <c r="C10" s="4" t="s">
         <v>211</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>14</v>
       </c>
-      <c r="B11" s="9">
+      <c r="B11" s="8">
         <v>1</v>
       </c>
-      <c r="C11" s="5" t="s">
+      <c r="C11" s="4" t="s">
         <v>205</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>14</v>
       </c>
-      <c r="B12" s="9">
+      <c r="B12" s="8">
         <v>2</v>
       </c>
-      <c r="C12" s="5" t="s">
+      <c r="C12" s="4" t="s">
         <v>206</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>14</v>
       </c>
-      <c r="B13" s="9">
+      <c r="B13" s="8">
         <v>3</v>
       </c>
-      <c r="C13" s="5" t="s">
+      <c r="C13" s="4" t="s">
         <v>207</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>14</v>
       </c>
-      <c r="B14" s="9">
+      <c r="B14" s="8">
         <v>4</v>
       </c>
-      <c r="C14" s="5" t="s">
+      <c r="C14" s="4" t="s">
         <v>208</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>14</v>
       </c>
-      <c r="B15" s="9">
+      <c r="B15" s="8">
         <v>5</v>
       </c>
-      <c r="C15" s="5" t="s">
+      <c r="C15" s="4" t="s">
         <v>209</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>14</v>
       </c>
-      <c r="B16" s="9">
+      <c r="B16" s="8">
         <v>6</v>
       </c>
-      <c r="C16" s="5" t="s">
+      <c r="C16" s="4" t="s">
         <v>210</v>
       </c>
     </row>
@@ -2692,10 +2691,10 @@
       <c r="A17" t="s">
         <v>14</v>
       </c>
-      <c r="B17" s="9">
+      <c r="B17" s="8">
         <v>7</v>
       </c>
-      <c r="C17" s="5" t="s">
+      <c r="C17" s="4" t="s">
         <v>211</v>
       </c>
     </row>
@@ -2714,10 +2713,10 @@
       <c r="A19" t="s">
         <v>29</v>
       </c>
-      <c r="B19" s="9">
+      <c r="B19" s="8">
         <v>2</v>
       </c>
-      <c r="C19" s="12" t="s">
+      <c r="C19" s="11" t="s">
         <v>201</v>
       </c>
     </row>
@@ -2725,10 +2724,10 @@
       <c r="A20" t="s">
         <v>29</v>
       </c>
-      <c r="B20" s="9">
+      <c r="B20" s="8">
         <v>3</v>
       </c>
-      <c r="C20" s="12" t="s">
+      <c r="C20" s="11" t="s">
         <v>202</v>
       </c>
     </row>
@@ -2736,10 +2735,10 @@
       <c r="A21" t="s">
         <v>29</v>
       </c>
-      <c r="B21" s="9">
+      <c r="B21" s="8">
         <v>4</v>
       </c>
-      <c r="C21" s="12" t="s">
+      <c r="C21" s="11" t="s">
         <v>203</v>
       </c>
     </row>
@@ -2747,186 +2746,186 @@
       <c r="A22" t="s">
         <v>29</v>
       </c>
-      <c r="B22" s="9">
+      <c r="B22" s="8">
         <v>5</v>
       </c>
-      <c r="C22" s="12" t="s">
+      <c r="C22" s="11" t="s">
         <v>204</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A23" s="5" t="s">
+      <c r="A23" s="4" t="s">
         <v>212</v>
       </c>
-      <c r="B23" s="3">
+      <c r="B23" s="2">
         <v>1</v>
       </c>
-      <c r="C23" s="5" t="s">
+      <c r="C23" s="4" t="s">
         <v>223</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A24" s="5" t="s">
+      <c r="A24" s="4" t="s">
         <v>212</v>
       </c>
-      <c r="B24" s="3">
+      <c r="B24" s="2">
         <v>2</v>
       </c>
-      <c r="C24" s="5" t="s">
+      <c r="C24" s="4" t="s">
         <v>222</v>
       </c>
     </row>
     <row r="25" spans="1:3" ht="30" x14ac:dyDescent="0.25">
-      <c r="A25" s="5" t="s">
+      <c r="A25" s="4" t="s">
         <v>212</v>
       </c>
-      <c r="B25" s="3">
+      <c r="B25" s="2">
         <v>3</v>
       </c>
-      <c r="C25" s="5" t="s">
+      <c r="C25" s="4" t="s">
         <v>221</v>
       </c>
     </row>
     <row r="26" spans="1:3" ht="30" x14ac:dyDescent="0.25">
-      <c r="A26" s="5" t="s">
+      <c r="A26" s="4" t="s">
         <v>212</v>
       </c>
-      <c r="B26" s="3">
+      <c r="B26" s="2">
         <v>4</v>
       </c>
-      <c r="C26" s="5" t="s">
+      <c r="C26" s="4" t="s">
         <v>216</v>
       </c>
     </row>
     <row r="27" spans="1:3" ht="30" x14ac:dyDescent="0.25">
-      <c r="A27" s="5" t="s">
+      <c r="A27" s="4" t="s">
         <v>212</v>
       </c>
-      <c r="B27" s="3">
+      <c r="B27" s="2">
         <v>5</v>
       </c>
-      <c r="C27" s="5" t="s">
+      <c r="C27" s="4" t="s">
         <v>217</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A28" s="5" t="s">
+      <c r="A28" s="4" t="s">
         <v>212</v>
       </c>
-      <c r="B28" s="3">
+      <c r="B28" s="2">
         <v>6</v>
       </c>
-      <c r="C28" s="5" t="s">
+      <c r="C28" s="4" t="s">
         <v>218</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A29" s="5" t="s">
+      <c r="A29" s="4" t="s">
         <v>212</v>
       </c>
-      <c r="B29" s="3">
+      <c r="B29" s="2">
         <v>7</v>
       </c>
-      <c r="C29" s="5" t="s">
+      <c r="C29" s="4" t="s">
         <v>219</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A30" s="5" t="s">
+      <c r="A30" s="4" t="s">
         <v>212</v>
       </c>
-      <c r="B30" s="3">
+      <c r="B30" s="2">
         <v>8</v>
       </c>
-      <c r="C30" s="5" t="s">
+      <c r="C30" s="4" t="s">
         <v>220</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A31" s="5" t="s">
+      <c r="A31" s="4" t="s">
         <v>213</v>
       </c>
-      <c r="B31" s="3">
+      <c r="B31" s="2">
         <v>1</v>
       </c>
-      <c r="C31" s="5" t="s">
+      <c r="C31" s="4" t="s">
         <v>223</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A32" s="5" t="s">
+      <c r="A32" s="4" t="s">
         <v>213</v>
       </c>
-      <c r="B32" s="3">
+      <c r="B32" s="2">
         <v>2</v>
       </c>
-      <c r="C32" s="5" t="s">
+      <c r="C32" s="4" t="s">
         <v>222</v>
       </c>
     </row>
-    <row r="33" spans="1:3" ht="30" x14ac:dyDescent="0.25">
-      <c r="A33" s="5" t="s">
+    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A33" s="4" t="s">
         <v>213</v>
       </c>
-      <c r="B33" s="3">
+      <c r="B33" s="2">
         <v>3</v>
       </c>
-      <c r="C33" s="5" t="s">
+      <c r="C33" s="4" t="s">
         <v>221</v>
       </c>
     </row>
-    <row r="34" spans="1:3" ht="30" x14ac:dyDescent="0.25">
-      <c r="A34" s="5" t="s">
+    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A34" s="4" t="s">
         <v>213</v>
       </c>
-      <c r="B34" s="3">
+      <c r="B34" s="2">
         <v>4</v>
       </c>
-      <c r="C34" s="5" t="s">
+      <c r="C34" s="4" t="s">
         <v>216</v>
       </c>
     </row>
-    <row r="35" spans="1:3" ht="30" x14ac:dyDescent="0.25">
-      <c r="A35" s="5" t="s">
+    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A35" s="4" t="s">
         <v>213</v>
       </c>
-      <c r="B35" s="3">
+      <c r="B35" s="2">
         <v>5</v>
       </c>
-      <c r="C35" s="5" t="s">
+      <c r="C35" s="4" t="s">
         <v>217</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A36" s="5" t="s">
+      <c r="A36" s="4" t="s">
         <v>213</v>
       </c>
-      <c r="B36" s="3">
+      <c r="B36" s="2">
         <v>6</v>
       </c>
-      <c r="C36" s="5" t="s">
+      <c r="C36" s="4" t="s">
         <v>218</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A37" s="5" t="s">
+      <c r="A37" s="4" t="s">
         <v>213</v>
       </c>
-      <c r="B37" s="3">
+      <c r="B37" s="2">
         <v>7</v>
       </c>
-      <c r="C37" s="5" t="s">
+      <c r="C37" s="4" t="s">
         <v>219</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A38" s="5" t="s">
+      <c r="A38" s="4" t="s">
         <v>213</v>
       </c>
-      <c r="B38" s="3">
+      <c r="B38" s="2">
         <v>8</v>
       </c>
-      <c r="C38" s="5" t="s">
+      <c r="C38" s="4" t="s">
         <v>220</v>
       </c>
     </row>
@@ -3177,15 +3176,6 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <Zeit xmlns="b63cdcf7-47fa-43f6-87e5-23b415b5c413" xsi:nil="true"/>
@@ -3195,6 +3185,15 @@
     <TaxCatchAll xmlns="12535b08-222e-45d2-b6db-15019f1afee6" xsi:nil="true"/>
   </documentManagement>
 </p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -3217,14 +3216,6 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4C05FF1B-7508-40EF-8319-E993EA07F007}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1D9CBEFE-8C4C-4054-8E02-CA457E93B4C8}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
@@ -3239,4 +3230,12 @@
     <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4C05FF1B-7508-40EF-8319-E993EA07F007}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>